--- a/setup_files/hpp_layout.xlsx
+++ b/setup_files/hpp_layout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bluepp-my.sharepoint.com/personal/xfsf_bpp-projects_com/Documents/Documents/GitHub/Speciale/input files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bluepp-my.sharepoint.com/personal/xfsf_bpp-projects_com/Documents/Documents/GitHub/Speciale/setup_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="339" documentId="8_{3A720C2A-8BB2-46CC-9A31-194013BDD676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AAA448A-3B8F-4902-8B52-8E7E079EC6BD}"/>
+  <xr:revisionPtr revIDLastSave="460" documentId="8_{3A720C2A-8BB2-46CC-9A31-194013BDD676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3672258-BA23-4408-9316-76862F1ED0D2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{7643C590-AB87-4ECC-9949-F1DE609BD7D2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7643C590-AB87-4ECC-9949-F1DE609BD7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Carriers" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,22 @@
     <author>Frederik Skou Fertin</author>
   </authors>
   <commentList>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{D8A9701D-5B57-471A-8F0C-1C9A2CC863BC}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{E4CB2F69-B3C5-478A-BCC4-1CAC1308E333}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Frederik Skou Fertin:
+Incompatible with '-' in the name of a unit.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{D8A9701D-5B57-471A-8F0C-1C9A2CC863BC}">
       <text>
         <r>
           <rPr>
@@ -64,7 +79,8 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-MWh/input</t>
+MWh/output for links.
+MWh/inflow for storages and offtakers.</t>
         </r>
       </text>
     </comment>
@@ -102,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{0BFF4858-E6D3-4475-B27D-FD3088427621}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{0BFF4858-E6D3-4475-B27D-FD3088427621}">
       <text>
         <r>
           <rPr>
@@ -126,6 +142,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{40EC406C-3811-46B7-8D89-66E3F9550F13}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Frederik Skou Fertin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Half of the NH3 capacity is contracted away.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -136,7 +176,7 @@
     <author>Frederik Skou Fertin</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{81CBFBB2-BCE5-440F-9F42-480A77FB4E74}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{81CBFBB2-BCE5-440F-9F42-480A77FB4E74}">
       <text>
         <r>
           <rPr>
@@ -165,7 +205,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="77">
   <si>
     <t>Electrolyzer</t>
   </si>
@@ -188,12 +228,6 @@
     <t>rate</t>
   </si>
   <si>
-    <t>reversible</t>
-  </si>
-  <si>
-    <t>charge_rate</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
@@ -203,18 +237,12 @@
     <t>solar</t>
   </si>
   <si>
-    <t>electricity</t>
-  </si>
-  <si>
     <t>WindPower</t>
   </si>
   <si>
     <t>wind</t>
   </si>
   <si>
-    <t>GCP</t>
-  </si>
-  <si>
     <t>link</t>
   </si>
   <si>
@@ -230,9 +258,6 @@
     <t>storage</t>
   </si>
   <si>
-    <t>Haber-Bosch Plant</t>
-  </si>
-  <si>
     <t>ammonia</t>
   </si>
   <si>
@@ -260,9 +285,6 @@
     <t>ammonia_offtake</t>
   </si>
   <si>
-    <t>electricity_offtake</t>
-  </si>
-  <si>
     <t>simulated</t>
   </si>
   <si>
@@ -272,9 +294,6 @@
     <t>nuclear</t>
   </si>
   <si>
-    <t>supplier</t>
-  </si>
-  <si>
     <t>offtaker</t>
   </si>
   <si>
@@ -290,9 +309,6 @@
     <t>annual_cf</t>
   </si>
   <si>
-    <t>baseload ppa</t>
-  </si>
-  <si>
     <t>Hydrogen1</t>
   </si>
   <si>
@@ -314,9 +330,6 @@
     <t>MW</t>
   </si>
   <si>
-    <t>grid</t>
-  </si>
-  <si>
     <t>AmmoniaSpot</t>
   </si>
   <si>
@@ -371,9 +384,6 @@
     <t>Ammonia synthesis rate is 5.5 tNH3/tH2. Electricity consumption for other processes is 1.65 MWh/tNH3.</t>
   </si>
   <si>
-    <t>Storage capacity is 31 days continuous maximum production. Small consumption for optimization.</t>
-  </si>
-  <si>
     <t>Shipment which is the main channel of ammonia offtake.</t>
   </si>
   <si>
@@ -381,6 +391,51 @@
   </si>
   <si>
     <t>Baseload PPA of 50 MW.</t>
+  </si>
+  <si>
+    <t>penalty</t>
+  </si>
+  <si>
+    <t>spot_contract</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>grid_electricity</t>
+  </si>
+  <si>
+    <t>plant_electricity</t>
+  </si>
+  <si>
+    <t>electricity_consumption</t>
+  </si>
+  <si>
+    <t>ElectricitySpot</t>
+  </si>
+  <si>
+    <t>spot_electricity</t>
+  </si>
+  <si>
+    <t>Capacity to allow for sale of all PPA, or buy of all GCP capacity.</t>
+  </si>
+  <si>
+    <t>availability</t>
+  </si>
+  <si>
+    <t>Haber Bosch Plant</t>
+  </si>
+  <si>
+    <t>Grid Connection Point</t>
+  </si>
+  <si>
+    <t>dayahead</t>
+  </si>
+  <si>
+    <t>ppa</t>
+  </si>
+  <si>
+    <t>Storage capacity is 31 days continuous maximum production. Small consumption for inflow, to avoid simultaneous in- and outflow.</t>
   </si>
 </sst>
 </file>
@@ -823,47 +878,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C94580FE-4FAA-4EB4-9011-2CE5D705C8AE}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="15.5703125" customWidth="1"/>
+    <col min="1" max="2" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -872,16 +935,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4227C92-656E-4719-8EA9-FD34C0DD0C21}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" customWidth="1"/>
+    <col min="1" max="5" width="15.54296875" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" customWidth="1"/>
+    <col min="8" max="8" width="24.453125" customWidth="1"/>
+    <col min="9" max="9" width="22.453125" customWidth="1"/>
+    <col min="10" max="10" width="34.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="4" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -892,7 +957,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
@@ -904,311 +969,627 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2">
+        <f>MAX(C3,SUM(PPAs!C2:C4))</f>
+        <v>650</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2">
+        <f>(C7*H7+H4*C4)*G3</f>
+        <v>556.875</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6">
+        <f>480/H4</f>
+        <v>8.9887640449438209</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="6">
+        <f>2/18</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="H4" s="2">
+        <v>53.4</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <f>1200/24</f>
+        <v>50</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="H7" s="2">
+        <f>0.3*G7</f>
+        <v>1.65</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2">
+        <f>C7*31*24</f>
+        <v>37200</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E2:F9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D653FE9-ECBC-4C18-ACB0-A1757BCB2761}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.54296875" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" customWidth="1"/>
+    <col min="3" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="21.54296875" customWidth="1"/>
+    <col min="11" max="12" width="17.81640625" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="7"/>
+    </row>
+    <row r="2" spans="1:13" ht="87" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="D2" s="2">
+        <f>4*C2</f>
+        <v>20000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="2">
+        <f>Components!C5</f>
+        <v>20</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2">
+        <v>900</v>
+      </c>
+      <c r="D3" s="2">
+        <f>4*C3</f>
+        <v>3600</v>
+      </c>
+      <c r="E3" s="2">
+        <f>Components!C7*8760/2</f>
+        <v>219000</v>
+      </c>
+      <c r="F3" s="2">
+        <f>Components!C9</f>
+        <v>25000</v>
+      </c>
+      <c r="G3" s="2">
+        <v>80000</v>
+      </c>
+      <c r="H3" s="2">
+        <v>80000</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2">
+        <v>450</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <f>Components!C9</f>
+        <v>25000</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2159F0F7-3B2A-4D06-AB40-89B8755A542A}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="10" max="10" width="20.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2">
         <v>400</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="6">
+        <v>65</v>
+      </c>
+      <c r="G2" s="2">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="I2" s="2">
         <v>1</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2">
         <v>200</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="6">
+        <v>65</v>
+      </c>
+      <c r="G3" s="2">
+        <v>40</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I3" s="2">
         <v>1</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2">
         <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="6">
+        <v>65</v>
+      </c>
+      <c r="G4" s="2">
+        <v>80</v>
+      </c>
+      <c r="H4" s="2">
         <v>1</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
       <c r="J4" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="2">
-        <f>C9*I9+C6/G6</f>
-        <v>562.5</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="6">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="6">
-        <f>480*G6</f>
-        <v>8.9887640449438209</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="6">
-        <f>1/53.4</f>
-        <v>1.8726591760299626E-2</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="2">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="6">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="6">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2">
-        <v>0.94</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2">
-        <f>1200/24</f>
-        <v>50</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="6">
-        <v>5.5</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2">
-        <f>0.3*G9</f>
-        <v>1.65</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="2">
-        <f>C9*31*24</f>
-        <v>37200</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="6">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2">
-        <v>25000</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="6">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F11">
+  <conditionalFormatting sqref="E2:F4">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1223,274 +1604,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D653FE9-ECBC-4C18-ACB0-A1757BCB2761}">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="8" width="15.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:11" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2000</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E2" s="2">
-        <f>Components!C7</f>
-        <v>20</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="2">
-        <v>900</v>
-      </c>
-      <c r="D3" s="2">
-        <v>80000</v>
-      </c>
-      <c r="E3" s="2">
-        <f>Components!C11</f>
-        <v>25000</v>
-      </c>
-      <c r="F3" s="2">
-        <v>80000</v>
-      </c>
-      <c r="G3" s="2">
-        <v>80000</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="2">
-        <v>300</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2">
-        <v>2000</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2159F0F7-3B2A-4D06-AB40-89B8755A542A}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="13.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2">
-        <v>400</v>
-      </c>
-      <c r="E2" s="2">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2">
-        <v>200</v>
-      </c>
-      <c r="E3" s="2">
-        <v>40</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2">
-        <v>80</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/setup_files/hpp_layout.xlsx
+++ b/setup_files/hpp_layout.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bluepp-my.sharepoint.com/personal/xfsf_bpp-projects_com/Documents/Documents/GitHub/Speciale/setup_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="8_{3A720C2A-8BB2-46CC-9A31-194013BDD676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3672258-BA23-4408-9316-76862F1ED0D2}"/>
+  <xr:revisionPtr revIDLastSave="639" documentId="8_{3A720C2A-8BB2-46CC-9A31-194013BDD676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41EC3D81-4894-4498-868F-9BE2E9A36F3F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7643C590-AB87-4ECC-9949-F1DE609BD7D2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{7643C590-AB87-4ECC-9949-F1DE609BD7D2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Carriers" sheetId="3" r:id="rId1"/>
-    <sheet name="Components" sheetId="1" r:id="rId2"/>
-    <sheet name="Contracts" sheetId="2" r:id="rId3"/>
-    <sheet name="PPAs" sheetId="5" r:id="rId4"/>
+    <sheet name="Scenarios" sheetId="7" r:id="rId1"/>
+    <sheet name="Carriers" sheetId="3" r:id="rId2"/>
+    <sheet name="Components" sheetId="1" r:id="rId3"/>
+    <sheet name="Contracts" sheetId="2" r:id="rId4"/>
+    <sheet name="PPAs" sheetId="5" r:id="rId5"/>
+    <sheet name="Annual Contract Summaries" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,6 +41,136 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Frederik Skou Fertin</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{38D2FF17-1B12-4FD8-892C-AC0D7AB10AA0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Frederik Skou Fertin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+What scenario is this change connected to?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{092117FD-972D-4BCE-A479-671B234E65FB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Frederik Skou Fertin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Is it (component, contract, ppa)?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{B1FA9018-3FD9-4F79-BBAF-DF9DBC1279C5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Frederik Skou Fertin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+What is the name of the thing changed?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{E3973579-80BC-4E93-968E-326BDA3061BA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Frederik Skou Fertin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+What is the Parameter changed (price, capacity, volume, etc)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{E0F45131-CAB8-45C4-95C5-85F58411B907}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Frederik Skou Fertin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+What is the new value in the scenario?</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Frederik Skou Fertin</author>
@@ -88,7 +220,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Frederik Skou Fertin</author>
@@ -170,7 +302,7 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Frederik Skou Fertin</author>
@@ -205,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="96">
   <si>
     <t>Electrolyzer</t>
   </si>
@@ -369,9 +501,6 @@
     <t>Solar power capacity is 400 MWp.</t>
   </si>
   <si>
-    <t>Wind power capacity is 200 MW.</t>
-  </si>
-  <si>
     <t>Capacity of 480 Mwe equals 8.99 tH2/h. Efficiency of 53.4 MWh/tH2.</t>
   </si>
   <si>
@@ -436,12 +565,75 @@
   </si>
   <si>
     <t>Storage capacity is 31 days continuous maximum production. Small consumption for inflow, to avoid simultaneous in- and outflow.</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>PPA</t>
+  </si>
+  <si>
+    <t>Power [GWh]</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Cost [M€]</t>
+  </si>
+  <si>
+    <t>Revenue [M€]</t>
+  </si>
+  <si>
+    <t>Changed Parameter</t>
+  </si>
+  <si>
+    <t>Changed Type</t>
+  </si>
+  <si>
+    <t>New Value</t>
+  </si>
+  <si>
+    <t>contract</t>
+  </si>
+  <si>
+    <t>Changed Object</t>
+  </si>
+  <si>
+    <t>80percent_ammonia</t>
+  </si>
+  <si>
+    <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>70percent_ammonia</t>
+  </si>
+  <si>
+    <t>60percent_ammonia</t>
+  </si>
+  <si>
+    <t>50percent_ammonia</t>
+  </si>
+  <si>
+    <t>40percent_ammonia</t>
+  </si>
+  <si>
+    <t>no_solar_power</t>
+  </si>
+  <si>
+    <t>high_RE_level</t>
+  </si>
+  <si>
+    <t>Wind power capacity is 300 MW.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -516,7 +708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -540,6 +732,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -877,6 +1074,202 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8993DA30-87E6-4FE5-BCAE-7905C7ABE8F6}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2">
+        <f>Components!C7*8760*0.8</f>
+        <v>350400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3">
+        <f>Components!C7*8760*0.7</f>
+        <v>306600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4">
+        <f>Components!C7*8760*0.6</f>
+        <v>262800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <f>Components!C7*8760*0.5</f>
+        <v>219000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <f>Components!C7*8760*0.4</f>
+        <v>175200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <f>PPAs!C3*1.5</f>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <f>PPAs!C2*1.5</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <f>PPAs!C3*1.5</f>
+        <v>450</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C94580FE-4FAA-4EB4-9011-2CE5D705C8AE}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -895,7 +1288,7 @@
     </row>
     <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>31</v>
@@ -922,7 +1315,7 @@
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>31</v>
@@ -933,7 +1326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4227C92-656E-4719-8EA9-FD34C0DD0C21}">
   <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -969,10 +1362,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>7</v>
@@ -980,23 +1373,23 @@
     </row>
     <row r="2" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2">
         <f>MAX(C3,SUM(PPAs!C2:C4))</f>
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2" s="6">
         <v>1</v>
@@ -1008,12 +1401,12 @@
         <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -1026,10 +1419,10 @@
         <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="G3" s="6">
         <v>0.99</v>
@@ -1041,7 +1434,7 @@
         <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -1059,7 +1452,7 @@
         <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
@@ -1075,7 +1468,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -1107,7 +1500,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -1139,12 +1532,12 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -1173,7 +1566,7 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -1206,7 +1599,7 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -1238,7 +1631,7 @@
         <v>38</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1260,7 +1653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D653FE9-ECBC-4C18-ACB0-A1757BCB2761}">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1284,7 +1677,7 @@
         <v>20</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>21</v>
@@ -1308,7 +1701,7 @@
         <v>36</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M1" s="7"/>
     </row>
@@ -1417,7 +1810,8 @@
         <v>25000</v>
       </c>
       <c r="F4" s="2">
-        <v>2000</v>
+        <f>Components!C9</f>
+        <v>25000</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -1449,7 +1843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2159F0F7-3B2A-4D06-AB40-89B8755A542A}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1497,7 +1891,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2">
         <v>400</v>
@@ -1509,13 +1903,13 @@
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
@@ -1529,10 +1923,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>40</v>
@@ -1541,19 +1935,19 @@
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3" s="2">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H3" s="2">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="I3" s="2">
         <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -1561,7 +1955,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2">
         <v>50</v>
@@ -1573,10 +1967,10 @@
         <v>28</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -1585,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1604,4 +1998,137 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF48DFE2-21C8-4CC0-B4F1-F354F2538655}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="str">
+        <f>PPAs!A2</f>
+        <v>SolarPower</v>
+      </c>
+      <c r="B2" s="10">
+        <f>PPAs!C2*PPAs!H2*8760/1000</f>
+        <v>630.72</v>
+      </c>
+      <c r="C2" s="9">
+        <f>B2*PPAs!G2/1000</f>
+        <v>22.075200000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="str">
+        <f>PPAs!A3</f>
+        <v>WindPower</v>
+      </c>
+      <c r="B3" s="10">
+        <f>PPAs!C3*PPAs!H3*8760/1000</f>
+        <v>998.64</v>
+      </c>
+      <c r="C3" s="9">
+        <f>B3*PPAs!G3/1000</f>
+        <v>54.925199999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="str">
+        <f>PPAs!A4</f>
+        <v>NuclearPower</v>
+      </c>
+      <c r="B4" s="10">
+        <f>PPAs!C4*PPAs!H4*8760/1000</f>
+        <v>438</v>
+      </c>
+      <c r="C4" s="9">
+        <f>B4*PPAs!G4/1000</f>
+        <v>30.66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="12">
+        <f>SUM(B2:B4)</f>
+        <v>2067.36</v>
+      </c>
+      <c r="C5" s="13">
+        <f>SUM(C2:C4)</f>
+        <v>107.6604</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="str">
+        <f>Contracts!A2</f>
+        <v>Hydrogen1</v>
+      </c>
+      <c r="B8" s="10">
+        <f>Contracts!E2*Components!H4/Components!G3*8760/1000</f>
+        <v>236.25454545454545</v>
+      </c>
+      <c r="C8">
+        <f>Contracts!E2*Contracts!C2*8760/1000000</f>
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="str">
+        <f>Contracts!A3</f>
+        <v>Ammonia1</v>
+      </c>
+      <c r="B9" s="10">
+        <f>Contracts!E3*(Components!H7+Components!H4/Components!G7)/Components!G3/1000</f>
+        <v>2512.7685950413224</v>
+      </c>
+      <c r="C9">
+        <f>Contracts!E3*Contracts!C3/1000000</f>
+        <v>197.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="12">
+        <f>SUM(B8:B9)</f>
+        <v>2749.0231404958677</v>
+      </c>
+      <c r="C10" s="12">
+        <f>SUM(C8:C9)</f>
+        <v>219</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/setup_files/hpp_layout.xlsx
+++ b/setup_files/hpp_layout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bluepp-my.sharepoint.com/personal/xfsf_bpp-projects_com/Documents/Documents/GitHub/Speciale/setup_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="639" documentId="8_{3A720C2A-8BB2-46CC-9A31-194013BDD676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41EC3D81-4894-4498-868F-9BE2E9A36F3F}"/>
+  <xr:revisionPtr revIDLastSave="684" documentId="8_{3A720C2A-8BB2-46CC-9A31-194013BDD676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17EBA078-FEB5-4E42-9A32-1954A6679847}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{7643C590-AB87-4ECC-9949-F1DE609BD7D2}"/>
+    <workbookView xWindow="120" yWindow="2690" windowWidth="14400" windowHeight="8170" activeTab="4" xr2:uid="{7643C590-AB87-4ECC-9949-F1DE609BD7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="7" r:id="rId1"/>
@@ -54,7 +54,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -63,7 +63,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 What scenario is this change connected to?</t>
@@ -78,7 +78,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -87,7 +87,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Is it (component, contract, ppa)?</t>
@@ -102,7 +102,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -111,7 +111,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 What is the name of the thing changed?</t>
@@ -126,7 +126,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -135,7 +135,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 What is the Parameter changed (price, capacity, volume, etc)</t>
@@ -150,7 +150,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -159,7 +159,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 What is the new value in the scenario?</t>
@@ -184,7 +184,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:
 Incompatible with '-' in the name of a unit.</t>
@@ -199,7 +199,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -208,7 +208,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 MWh/output for links.
@@ -234,7 +234,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -243,7 +243,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 €/t</t>
@@ -258,7 +258,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -267,7 +267,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Shipment capacity upper bound.</t>
@@ -282,7 +282,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -291,7 +291,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Half of the NH3 capacity is contracted away.</t>
@@ -316,7 +316,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Frederik Skou Fertin:</t>
         </r>
@@ -325,7 +325,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 €/MWh</t>
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="100">
   <si>
     <t>Electrolyzer</t>
   </si>
@@ -625,6 +625,18 @@
   </si>
   <si>
     <t>Wind power capacity is 300 MW.</t>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>30percent_ammonia</t>
+  </si>
+  <si>
+    <t>20percent_ammonia</t>
+  </si>
+  <si>
+    <t>base_case_no_spot</t>
   </si>
 </sst>
 </file>
@@ -654,14 +666,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1075,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8993DA30-87E6-4FE5-BCAE-7905C7ABE8F6}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
@@ -1122,145 +1134,287 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>89</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>85</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <f>Components!C7*8760*0.7</f>
         <v>306600</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>85</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>21</v>
       </c>
-      <c r="E4">
+      <c r="E6">
         <f>Components!C7*8760*0.6</f>
         <v>262800</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>91</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="E5">
+      <c r="E7">
         <f>Components!C7*8760*0.5</f>
         <v>219000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>92</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>85</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D8" t="s">
         <v>21</v>
       </c>
-      <c r="E6">
+      <c r="E8">
         <f>Components!C7*8760*0.4</f>
         <v>175200</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <f>Components!C7*8760*0.3</f>
+        <v>131400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <f>Components!C7*8760*0.2</f>
+        <v>87600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B11" t="s">
         <v>74</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D11" t="s">
         <v>3</v>
       </c>
-      <c r="E7">
+      <c r="E11">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>93</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B12" t="s">
         <v>74</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D12" t="s">
         <v>3</v>
       </c>
-      <c r="E8">
+      <c r="E12">
         <f>PPAs!C3*1.5</f>
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13">
+        <f>Components!C$7*8760*0.3</f>
+        <v>131400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>94</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B14" t="s">
         <v>74</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C14" t="s">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D14" t="s">
         <v>3</v>
       </c>
-      <c r="E9">
+      <c r="E14">
         <f>PPAs!C2*1.5</f>
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>94</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B15" t="s">
         <v>74</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D15" t="s">
         <v>3</v>
       </c>
-      <c r="E10">
+      <c r="E15">
         <f>PPAs!C3*1.5</f>
         <v>450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <f>E15+E14+PPAs!C4</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17">
+        <f>Components!C$7*8760*0.3</f>
+        <v>131400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18">
+        <f>Components!C$7*8760*0.3</f>
+        <v>131400</v>
       </c>
     </row>
   </sheetData>
@@ -1906,7 +2060,7 @@
         <v>64</v>
       </c>
       <c r="G2" s="2">
-        <v>35</v>
+        <v>55.2</v>
       </c>
       <c r="H2" s="2">
         <v>0.18</v>
@@ -1938,7 +2092,7 @@
         <v>64</v>
       </c>
       <c r="G3" s="2">
-        <v>55</v>
+        <v>66.2</v>
       </c>
       <c r="H3" s="2">
         <v>0.38</v>
@@ -1970,7 +2124,7 @@
         <v>64</v>
       </c>
       <c r="G4" s="2">
-        <v>70</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -2032,7 +2186,7 @@
       </c>
       <c r="C2" s="9">
         <f>B2*PPAs!G2/1000</f>
-        <v>22.075200000000002</v>
+        <v>34.815744000000009</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2046,7 +2200,7 @@
       </c>
       <c r="C3" s="9">
         <f>B3*PPAs!G3/1000</f>
-        <v>54.925199999999997</v>
+        <v>66.109968000000009</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2060,7 +2214,7 @@
       </c>
       <c r="C4" s="9">
         <f>B4*PPAs!G4/1000</f>
-        <v>30.66</v>
+        <v>33.901200000000003</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2073,7 +2227,7 @@
       </c>
       <c r="C5" s="13">
         <f>SUM(C2:C4)</f>
-        <v>107.6604</v>
+        <v>134.82691200000002</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
